--- a/01_Reporting_Suite/Coates_Report_Recipients.xlsx
+++ b/01_Reporting_Suite/Coates_Report_Recipients.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -562,6 +562,7 @@
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -3189,6 +3190,524 @@
       <c r="F78" t="inlineStr">
         <is>
           <t>COMPANY,DEMOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>INDUSTEC FILTRATION</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Admin (Industec)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>admin@industec.com.au</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>COMPANY</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>From John Pickels 28 Jul 2026 - shared Industec/Filtercare inbox</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>FILTERCARE</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Admin (Industec &amp; Filtercare)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>admin@industec.com.au</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>COMPANY</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>From John Pickels 28 Jul 2026 - shared Industec/Filtercare inbox</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>INDUSTRIAL RESCUE &amp; EMERGENCY TRAINING</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Chris Short</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>chris.short@iretcq.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>COMPANY</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>From John Pickels 28 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BOSCH</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Gerhardus Van Der Westhuizen</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>gerhardus.vanderwesthuizen@boschrexroth.com.au</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>COMPANY</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>From John Pickels 28 Jul 2026 - not in SiteIQ yet; confirm the company spelling when Bosch holds gear</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>CUTRITE</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Matt Campbell</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>matt@cutrite.net.au</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>COMPANY</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>From John Pickels 28 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>David Moore</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>david.moore@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Cement master email 28 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Benjamin Vandenbroek</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>benjamin.vandenbroek@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Cement master email 28 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>John Pickels</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Cement master email 28 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Carmen Groat</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>carmen.groat@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Cement master email 28 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Hazel Barba</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>hazel.barba@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Cement master email 28 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Grant Holdsworth</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>grant.holdsworth@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Cement master email 28 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Daniel Osborne</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>daniel.osborne@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Cement master email 28 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Aaron Watts</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>aaron.watts@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Cement master email 28 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Adam McInnes</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Adam.McInnes@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Cement master email 28 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -3695,7 +4214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3738,7 +4257,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/01_Reporting_Suite/Coates_Report_Recipients.xlsx
+++ b/01_Reporting_Suite/Coates_Report_Recipients.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,6 @@
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -623,7 +622,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -633,7 +632,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Shutdown Manager - Coates Tool Store | 0429 352 788</t>
+          <t>Shutdown Manager - Coates Tool Store. OFF the reports 3 Aug 2026 (he sends them). Set Include=Yes to get a copy back.</t>
         </is>
       </c>
     </row>
@@ -3708,6 +3707,228 @@
       <c r="G92" t="inlineStr">
         <is>
           <t>Cement master email 28 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Industec Filtration</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>M Clayton</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>m.clayton@industec.com.au</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>COMPANY,DEMOB</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Site contact (from the routing workbook)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>John Pickels</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>COMPANY,DEMOB</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Cement Australia - standing Cc on every company report (Andrew, 3 Aug 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>David Moore</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>david.moore@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>COMPANY,DEMOB</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Cement Australia - standing Cc on every company report (Andrew, 3 Aug 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ben Vandenbroek</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>benjamin.vandenbroek@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>COMPANY,DEMOB</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Cement Australia - standing Cc on every company report (Andrew, 3 Aug 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Thomas Maher</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>COMPANY,DEMOB</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Coates - standing Cc on every company report (Andrew, 3 Aug 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Cody Mitchell</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>cody.mitchell@coates.com.au</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>COMPANY,DEMOB</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Coates - standing Cc on every company report (Andrew, 3 Aug 2026)</t>
         </is>
       </c>
     </row>

--- a/01_Reporting_Suite/Coates_Report_Recipients.xlsx
+++ b/01_Reporting_Suite/Coates_Report_Recipients.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3929,6 +3929,43 @@
       <c r="G98" t="inlineStr">
         <is>
           <t>Coates - standing Cc on every company report (Andrew, 3 Aug 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Industec Filtration</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Industec admin</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>admin@industec.com.au</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>COMPANY,DEMOB</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Site contact - Andrew, 3 Aug 2026</t>
         </is>
       </c>
     </row>

--- a/01_Reporting_Suite/Coates_Report_Recipients.xlsx
+++ b/01_Reporting_Suite/Coates_Report_Recipients.xlsx
@@ -3215,7 +3215,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>From John Pickels 28 Jul 2026 - shared Industec/Filtercare inbox</t>
+          <t>Site contact - switched on 3 Aug 2026 (Andrew)</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Site contact - Andrew, 3 Aug 2026</t>
+          <t>duplicate of row 79 - left off. Delete this row any time.</t>
         </is>
       </c>
     </row>

--- a/01_Reporting_Suite/Coates_Report_Recipients.xlsx
+++ b/01_Reporting_Suite/Coates_Report_Recipients.xlsx
@@ -3013,7 +3013,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Site Contact | 0459 106 376</t>
+          <t>Site Contact | 0459 106 376 | switched on 3 Aug 2026 (Andrew)</t>
         </is>
       </c>
     </row>
@@ -3050,12 +3050,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>COMPANY,DEMOB</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>switched on 3 Aug 2026 (Andrew)</t>
         </is>
       </c>
     </row>
@@ -3082,12 +3087,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>COMPANY,DEMOB</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>switched on 3 Aug 2026 (Andrew)</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3124,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3124,7 +3134,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Site Contact | 0447 031 824</t>
+          <t>Site Contact | 0447 031 824 | switched on 3 Aug 2026 (Andrew)</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3299,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3299,14 +3309,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>From John Pickels 28 Jul 2026</t>
+          <t>From John Pickels 28 Jul 2026 | switched on 3 Aug 2026 (Andrew)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BOSCH</t>
+          <t>BOSCH REXROTH</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3326,7 +3336,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3336,7 +3346,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>From John Pickels 28 Jul 2026 - not in SiteIQ yet; confirm the company spelling when Bosch holds gear</t>
+          <t>From John Pickels 28 Jul 2026 - not in SiteIQ yet; confirm the company spelling when Bosch holds gear | switched on 3 Aug 2026 (Andrew) | name was "BOSCH", corrected to SiteIQ spelling 3 Aug 2026</t>
         </is>
       </c>
     </row>

--- a/01_Reporting_Suite/Coates_Report_Recipients.xlsx
+++ b/01_Reporting_Suite/Coates_Report_Recipients.xlsx
@@ -930,7 +930,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>HSE | 0403 599 012</t>
+          <t>HSE | 0403 599 012 | OFF 3 Aug 2026 to match Andrew's sent items</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0477 527 326</t>
+          <t>0477 527 326 | OFF 3 Aug 2026 to match Andrew's sent items</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>HSEQ | 0458 536 151</t>
+          <t>HSEQ | 0458 536 151 | OFF 3 Aug 2026 to match Andrew's sent items</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Day Shift | 0437 445 837</t>
+          <t>Day Shift | 0437 445 837 | OFF 3 Aug 2026 to match Andrew's sent items</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Site Contact | 0431 403 640</t>
+          <t>Site Contact | 0431 403 640 | ON 3 Aug 2026 to match Andrew's sent items</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Night Shift | 0411 042 294</t>
+          <t>Night Shift | 0411 042 294 | OFF 3 Aug 2026 to match Andrew's sent items</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0422 133 223</t>
+          <t>0422 133 223 | OFF 3 Aug 2026 to match Andrew's sent items</t>
         </is>
       </c>
     </row>
@@ -2848,12 +2848,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>COMPANY,DEMOB</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ON 3 Aug 2026 to match Andrew's sent items</t>
         </is>
       </c>
     </row>
@@ -2880,12 +2885,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>COMPANY,DEMOB</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>ON 3 Aug 2026 to match Andrew's sent items</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3097,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3097,7 +3107,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>switched on 3 Aug 2026 (Andrew)</t>
+          <t>switched on 3 Aug 2026 (Andrew) | OFF 3 Aug 2026 to match Andrew's sent items</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3171,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>COMPANY,DEMOB</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ON 3 Aug 2026 to match Andrew's sent items</t>
         </is>
       </c>
     </row>
@@ -3193,12 +3208,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>COMPANY,DEMOB</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ON 3 Aug 2026 to match Andrew's sent items</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3393,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3383,7 +3403,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>From John Pickels 28 Jul 2026</t>
+          <t>From John Pickels 28 Jul 2026 | ON 3 Aug 2026 to match Andrew's sent items</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3763,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3753,7 +3773,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Site contact (from the routing workbook)</t>
+          <t>Site contact (from the routing workbook) | OFF 3 Aug 2026 to match Andrew's sent items</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3985,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3975,7 +3995,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>duplicate of row 79 - left off. Delete this row any time.</t>
+          <t>duplicate of row 79 - left off. Delete this row any time. | ON 3 Aug 2026 to match Andrew's sent items</t>
         </is>
       </c>
     </row>

--- a/01_Reporting_Suite/Coates_Report_Recipients.xlsx
+++ b/01_Reporting_Suite/Coates_Report_Recipients.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3996,6 +3996,43 @@
       <c r="G99" t="inlineStr">
         <is>
           <t>duplicate of row 79 - left off. Delete this row any time. | ON 3 Aug 2026 to match Andrew's sent items</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AESTEC</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Aestec accounts</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>accounts@aestec.com.au</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>COMPANY,DEMOB</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>from Andrew's sent items, 3 Aug 2026 - one To, standard Cc</t>
         </is>
       </c>
     </row>
